--- a/docs/무제체스_증강표_v2.xlsx
+++ b/docs/무제체스_증강표_v2.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="밸런스메모" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'증강목록'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'증강목록'!$A$1:$I$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -178,15 +178,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1022,7 +1022,7 @@
       </c>
     </row>
     <row r="22" ht="62" customHeight="1">
-      <c r="A22" s="7" t="n"/>
+      <c r="A22" s="10" t="n"/>
       <c r="B22" s="9" t="inlineStr">
         <is>
           <t>[K1c] 자신의 모든 제거를 처치로 간주합니다.</t>
@@ -1044,79 +1044,68 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="62" customHeight="1">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>[K1d] 이후 모든 강화에 필요한 처치 기물 수가 1 줄어듭니다. (1·3·6·11 → 0·2·5·10)</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>범례</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>범례</t>
+          <t>턴제한</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>정해진 턴 수 동안만 유효</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>턴제한</t>
+          <t>횟수제한</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>정해진 턴 수 동안만 유효</t>
+          <t>자신이 원할 때 정해진 횟수만큼 사용</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>횟수제한</t>
+          <t>영구지속</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>자신이 원할 때 정해진 횟수만큼 사용</t>
+          <t>게임이 끝날 때까지 유지</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>영구지속</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>게임이 끝날 때까지 유지</t>
+          <t>즉시 1회 처리 후 소멸</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>즉시 1회 처리 후 소멸</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
           <t>개정됨</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>원안에서 문구/수치가 수정된 증강</t>
         </is>
@@ -1127,8 +1116,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A14:A16"/>
   </mergeCells>
@@ -1142,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1204,163 +1193,163 @@
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
+      <c r="A2" s="17" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="17" t="n"/>
+      <c r="I2" s="17" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>P1a</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr"/>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr"/>
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 지정한 자신의 폰 하나가 지정불가 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
+      <c r="I3" s="17" t="inlineStr"/>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>P1b</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr"/>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>다음 1회, 폰이 두 번 전진할 수 있습니다. (전진할 곳에 다른 기물이 있을 시 움직일 수 없습니다.)</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr"/>
+      <c r="I4" s="17" t="inlineStr"/>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>P1c</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr"/>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr"/>
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>적을 처치한 폰이 다음 상대턴 동안, 가장 가까운 상대 폰과 함께 포영됩니다.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr"/>
+      <c r="I5" s="17" t="inlineStr"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>P3a</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr"/>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>내 다음 2턴 동안, 폰으로 다른 기물을 처치할 시 처치 카운팅이 2배로 적용됩니다.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr"/>
+      <c r="I6" s="17" t="inlineStr"/>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -1404,41 +1393,41 @@
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>P3c</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>폰이 적 기물을 처치한 후 원래 자리로 돌아올 수 있습니다. (선택 사항)</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr"/>
+      <c r="I8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -1482,41 +1471,41 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>P6b</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr"/>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>폰이 정면에 있는 적 기물도 처치할 수 있습니다.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr"/>
+      <c r="I10" s="17" t="inlineStr"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -1601,41 +1590,41 @@
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>P11b</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr"/>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr"/>
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>내 다음 3턴 동안, 지정한 폰을 퀸으로 변경합니다. 3턴 후, 그 폰은 제거됩니다.</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -1679,41 +1668,41 @@
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>R1a</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr"/>
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>룩이 기물을 최대 하나까지 통과할 수 있습니다.</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr"/>
+      <c r="I15" s="17" t="inlineStr"/>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -1757,152 +1746,152 @@
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>R1c</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr"/>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr"/>
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>내 다음 2턴 동안, 적을 처치한 룩과 지정한 상대 기물 하나가 지정불가 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="I17" s="17" t="inlineStr"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>R3a</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr"/>
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치하지는 못합니다.)</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr"/>
+      <c r="I18" s="17" t="inlineStr"/>
     </row>
     <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>R3b</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr"/>
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>다음 2턴 동안, 룩이 처치한 기물과 동일한 종류의 상대 기물을 모두 포영 상태로 만듭니다.</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="17" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>R3c</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>룩이 제거, 포영, 교환, 지정불가 효과에 면역이 됩니다.</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr"/>
+      <c r="I20" s="17" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -1987,78 +1976,78 @@
       </c>
     </row>
     <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>R6c</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>지정한 아군 룩과 상대 폰의 위치를 교환합니다.</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr"/>
+      <c r="I23" s="17" t="inlineStr"/>
     </row>
     <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>R11a</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>룩이 기물을 최대 두 개까지 통과할 수 있습니다.</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr"/>
+      <c r="I24" s="17" t="inlineStr"/>
     </row>
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -2143,78 +2132,78 @@
       </c>
     </row>
     <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>N1a</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr"/>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 지정한 아군 나이트가 지정불가 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr"/>
+      <c r="I27" s="17" t="inlineStr"/>
     </row>
     <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>N1b</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr"/>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>적을 처치한 나이트와 자신의 비숍 중 하나의 위치를 교환합니다.</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr"/>
+      <c r="I28" s="17" t="inlineStr"/>
     </row>
     <row r="29" ht="48" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -2422,115 +2411,115 @@
       </c>
     </row>
     <row r="34" ht="48" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>N6b</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="C34" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr"/>
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>상대 나이트와 내 나이트의 위치가 가로·세로 모두 5칸 이상 차이날 경우, 상대 나이트를 처치합니다. (대상이 여러 개일 경우 자신이 선택)</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr"/>
+      <c r="I34" s="17" t="inlineStr"/>
     </row>
     <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>N6c</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C35" s="11" t="n">
+      <c r="C35" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr"/>
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>즉시, 나이트가 킹과 퀸을 제외한 상대의 가장 낮은 점수의 기물을 하나 없애고 그 위치로 이동합니다. (여러 개일 시 자신이 선택)</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr"/>
+      <c r="I35" s="17" t="inlineStr"/>
     </row>
     <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>N11a</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C36" s="11" t="n">
+      <c r="C36" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr"/>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr"/>
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>나이트를 2회 이상 강화한 상태라면, 비어있는 칸에 1턴 동안 지정불가 상태인 나이트를 2개 소환합니다.</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr"/>
+      <c r="I36" s="17" t="inlineStr"/>
     </row>
     <row r="37" ht="48" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -2574,41 +2563,41 @@
       </c>
     </row>
     <row r="38" ht="48" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>N11c</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="C38" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr"/>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr"/>
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>자신의 나이트가 살아있고 상대의 퀸이 살아있다면, 두 기물 모두 제거합니다.</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr"/>
+      <c r="I38" s="17" t="inlineStr"/>
     </row>
     <row r="39" ht="48" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
@@ -2701,45 +2690,45 @@
       </c>
     </row>
     <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>B1c</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C41" s="11" t="n">
+      <c r="C41" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>다음 상대의 2턴 동안 지정한 상대 폰이 한 번도 움직이지 않았을 경우, 그 폰을 제거합니다.</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="G41" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr"/>
+      <c r="I41" s="17" t="inlineStr"/>
     </row>
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
@@ -2832,127 +2821,127 @@
       </c>
     </row>
     <row r="44" ht="48" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>B3c</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="C44" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F44" s="17" t="inlineStr">
         <is>
           <t>적을 처치한 비숍이 1턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G44" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H44" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr"/>
+      <c r="I44" s="17" t="inlineStr"/>
     </row>
     <row r="45" ht="48" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>B6a</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C45" s="11" t="n">
+      <c r="C45" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F45" s="17" t="inlineStr">
         <is>
           <t>상대의 다음 2턴 동안, 비숍이 처치당할 경우 비숍을 처치한 상대 기물도 같이 죽습니다. (킹·퀸 제외)</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G45" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr"/>
+      <c r="I45" s="17" t="inlineStr"/>
     </row>
     <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>B6b</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C46" s="11" t="n">
+      <c r="C46" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F46" s="17" t="inlineStr">
         <is>
           <t>상대의 다음 1턴 동안, 지정한 상대 기물이 움직이지 않는다면 제거됩니다. (킹·퀸 제외)</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G46" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H46" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr"/>
+      <c r="I46" s="17" t="inlineStr"/>
     </row>
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
@@ -3000,86 +2989,86 @@
       </c>
     </row>
     <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>B11a</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C48" s="11" t="n">
+      <c r="C48" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F48" s="17" t="inlineStr">
         <is>
           <t>다음 1회 아군 킹이 체크를 당할 때, 체크를 한 기물을 1턴 동안 지정불가 상태로 만듭니다.</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G48" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H48" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr"/>
+      <c r="I48" s="17" t="inlineStr"/>
     </row>
     <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>B11b</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C49" s="11" t="n">
+      <c r="C49" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F49" s="17" t="inlineStr">
         <is>
           <t>아군 퀸이 죽은 상태라면 내 다음 3턴 동안, 비숍이 퀸처럼 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="G49" s="11" t="inlineStr">
+      <c r="G49" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H49" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr"/>
+      <c r="I49" s="17" t="inlineStr"/>
     </row>
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
@@ -3168,41 +3157,41 @@
       </c>
     </row>
     <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Q1b</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C52" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>턴제한</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr"/>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr"/>
+      <c r="F52" s="17" t="inlineStr">
         <is>
           <t>내 다음 5턴 동안, 퀸이 상대 퀸과 함께 지정불가 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H52" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr"/>
+      <c r="I52" s="17" t="inlineStr"/>
     </row>
     <row r="53" ht="48" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
@@ -3287,78 +3276,78 @@
       </c>
     </row>
     <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>Q3b</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C55" s="11" t="n">
+      <c r="C55" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr"/>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr"/>
+      <c r="F55" s="17" t="inlineStr">
         <is>
           <t>다음 1회, 다음 상대턴 동안 아군 퀸을 포영 상태로 만듭니다.</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H55" s="11" t="inlineStr">
+      <c r="H55" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr"/>
+      <c r="I55" s="17" t="inlineStr"/>
     </row>
     <row r="56" ht="48" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>Q3c</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C56" s="11" t="n">
+      <c r="C56" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr"/>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr"/>
+      <c r="F56" s="17" t="inlineStr">
         <is>
           <t>이 게임에서 아군 퀸을 상대방이 처치해도 상대의 처치 카운트에 더해지지 않습니다.</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
+      <c r="G56" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H56" s="11" t="inlineStr">
+      <c r="H56" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I56" s="11" t="inlineStr"/>
+      <c r="I56" s="17" t="inlineStr"/>
     </row>
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
@@ -3402,78 +3391,78 @@
       </c>
     </row>
     <row r="58" ht="48" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>Q6b</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C58" s="11" t="n">
+      <c r="C58" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr"/>
-      <c r="F58" s="11" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr"/>
+      <c r="F58" s="17" t="inlineStr">
         <is>
           <t>퀸을 1회 이상 강화한 상태라면, 퀸이 나이트처럼도 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H58" s="11" t="inlineStr">
+      <c r="H58" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr"/>
+      <c r="I58" s="17" t="inlineStr"/>
     </row>
     <row r="59" ht="48" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>Q6c</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C59" s="11" t="n">
+      <c r="C59" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr"/>
-      <c r="F59" s="11" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr"/>
+      <c r="F59" s="17" t="inlineStr">
         <is>
           <t>아군 퀸이 킹을 제외한 상대의 가장 높은 점수의 기물과 위치가 교환됩니다.</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G59" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H59" s="11" t="inlineStr">
+      <c r="H59" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I59" s="11" t="inlineStr"/>
+      <c r="I59" s="17" t="inlineStr"/>
     </row>
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -3599,120 +3588,120 @@
       </c>
     </row>
     <row r="63" ht="48" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>K1a</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C63" s="11" t="n">
+      <c r="C63" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr"/>
-      <c r="F63" s="11" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr"/>
+      <c r="F63" s="17" t="inlineStr">
         <is>
           <t>다음 1회, 킹이 체크를 당한 경우 퀸과 킹의 위치를 바꿀 수 있습니다.</t>
         </is>
       </c>
-      <c r="G63" s="11" t="inlineStr">
+      <c r="G63" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr">
+      <c r="H63" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr"/>
+      <c r="I63" s="17" t="inlineStr"/>
     </row>
     <row r="64" ht="48" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>K1b</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C64" s="11" t="n">
+      <c r="C64" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr"/>
-      <c r="F64" s="11" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr"/>
+      <c r="F64" s="17" t="inlineStr">
         <is>
           <t>자신의 다음 강화에서 선택지를 두 개 고를 수 있습니다.</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G64" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H64" s="11" t="inlineStr">
+      <c r="H64" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr"/>
+      <c r="I64" s="17" t="inlineStr"/>
     </row>
     <row r="65" ht="48" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>K1c</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C65" s="11" t="n">
+      <c r="C65" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr"/>
-      <c r="F65" s="11" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr"/>
+      <c r="F65" s="17" t="inlineStr">
         <is>
           <t>자신의 모든 제거를 처치로 간주합니다.</t>
         </is>
       </c>
-      <c r="G65" s="11" t="inlineStr">
+      <c r="G65" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H65" s="11" t="inlineStr">
+      <c r="H65" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr"/>
+      <c r="I65" s="17" t="inlineStr"/>
     </row>
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>K1d</t>
+          <t>K3a</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -3721,195 +3710,195 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>영구지속</t>
+          <t>횟수제한</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>이후 모든 강화에 필요한 처치 기물 수가 1 줄어듭니다. (1·3·6·11 → 0·2·5·10)</t>
+          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>[신규] 사용자 제안 - 킹 증강 철학 예시</t>
+          <t>나이트, 비숍 중 한 기물의 3번째 강화 효과를 선택해 강화합니다.</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
+          <t>대상지정</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>개정</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="48" customHeight="1">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>K3b</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="inlineStr"/>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>상대 기물과 내 기물의 점수 차이만큼, 원하는 기물을 킹의 상하좌우에 배치할 수 있습니다. (상하좌우에 다른 기물이 있다면 그 칸에는 배치 불가)</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>(동일)</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>대상지정</t>
+        </is>
+      </c>
+      <c r="I67" s="17" t="inlineStr"/>
+    </row>
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>K3c</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>룩, 퀸 중 한 기물의 6번째 강화 효과를 선택해 강화합니다.</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>대상지정</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>개정</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="48" customHeight="1">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>K6a</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr"/>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>다음 1회, 다른 기물과 함께 킹을 한 번 움직일 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>(동일)</t>
+        </is>
+      </c>
+      <c r="H69" s="17" t="inlineStr">
+        <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I66" s="6" t="inlineStr">
+      <c r="I69" s="17" t="inlineStr"/>
+    </row>
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>K6b</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>횟수제한</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>킹이 두 칸씩 움직일 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>대상지정</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>개정</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="48" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>K3a</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr"/>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화 효과를 선택해 강화합니다.</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>대상지정</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>개정</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="48" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>K3b</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr"/>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>상대 기물과 내 기물의 점수 차이만큼, 원하는 기물을 킹의 상하좌우에 배치할 수 있습니다. (상하좌우에 다른 기물이 있다면 그 칸에는 배치 불가)</t>
-        </is>
-      </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>(동일)</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr">
-        <is>
-          <t>대상지정</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69" ht="48" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>K3c</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr"/>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>룩, 퀸 중 한 기물의 6번째 강화 효과를 선택해 강화합니다.</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>대상지정</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>개정</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="48" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>K6a</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr"/>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>다음 1회, 다른 기물과 함께 킹을 한 번 움직일 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>(동일)</t>
-        </is>
-      </c>
-      <c r="H70" s="11" t="inlineStr">
-        <is>
-          <t>자동</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr"/>
     </row>
     <row r="71" ht="48" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>K6b</t>
+          <t>K6c</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -3928,12 +3917,12 @@
       <c r="E71" s="6" t="inlineStr"/>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
+          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>킹이 두 칸씩 움직일 수 있습니다.</t>
+          <t>킹이 퀸처럼 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -3948,163 +3937,122 @@
       </c>
     </row>
     <row r="72" ht="48" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>K6c</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>K11a</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C72" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="C72" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr"/>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>킹이 퀸처럼 움직일 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr"/>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>킹이 아군 폰 하나를 상하로 지정한 위치까지 이동시킵니다. (기물을 넘어서는 갈 수 없습니다.)</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>(동일)</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
+      <c r="I72" s="17" t="inlineStr"/>
+    </row>
+    <row r="73" ht="48" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>K11b</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>영구지속</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>킹으로 3개의 기물을 더 처치하면 새로운 증강이 제시됩니다 (=이 게임에서 승리합니다)</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>자동</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>개정</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="48" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>K11a</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>K11c</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C73" s="11" t="n">
+      <c r="C74" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D73" s="11" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>횟수제한</t>
         </is>
       </c>
-      <c r="E73" s="11" t="inlineStr"/>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>킹이 아군 폰 하나를 상하로 지정한 위치까지 이동시킵니다. (기물을 넘어서는 갈 수 없습니다.)</t>
-        </is>
-      </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr"/>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>서로의 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
         <is>
           <t>(동일)</t>
         </is>
       </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>대상지정</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="inlineStr"/>
-    </row>
-    <row r="74" ht="48" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>K11b</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>영구지속</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr"/>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>킹으로 3개의 기물을 더 처치하면 새로운 증강이 제시됩니다 (=이 게임에서 승리합니다)</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="H74" s="17" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>개정</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="48" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>K11c</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>횟수제한</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr"/>
-      <c r="F75" s="11" t="inlineStr">
-        <is>
-          <t>서로의 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
-        </is>
-      </c>
-      <c r="G75" s="11" t="inlineStr">
-        <is>
-          <t>(동일)</t>
-        </is>
-      </c>
-      <c r="H75" s="11" t="inlineStr">
-        <is>
-          <t>자동</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr"/>
+      <c r="I74" s="17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I75"/>
+  <autoFilter ref="A1:I74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4115,7 +4063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4159,1058 +4107,1028 @@
       </c>
     </row>
     <row r="2" ht="66" customHeight="1">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
+      <c r="A2" s="17" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3" ht="66" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>P3b</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>폰이 뒤로도 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>폰이 뒤로도 움직일 수 있습니다. (뒤로는 처치할 수 없습니다.)</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>후진 처치 가능 여부가 미정의. 전진 규칙(정면 처치 불가)과 대칭이 되도록 '후진 처치 불가'로 명확화.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>P6a</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>폰이 좌우로 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>폰이 좌우로 움직일 수 있습니다. (좌우로는 처치할 수 없으며, 앙파상 대상이 되지 않습니다.)</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>좌우 이동 시 처치/앙파상 처리가 미정의라 규칙 충돌. 이동 전용으로 명확화.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>P6c</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>방금 적을 처치한 폰 전방 2칸 이내에 적 기물이 있을 시 교환합니다. 이때, 상대 기물의 기물점수가 더 높다면 그 기물을 폰으로 변이시킵니다.</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>적을 처치한 폰의 전방 2칸 이내에 적 기물이 있을 시 교환합니다. 이때 상대 기물의 기물점수가 더 높다면 그 기물을 폰으로 변이시킵니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>킹 예외 명시. 미명시 시 상대 킹을 폰으로 변이시켜 게임이 붕괴됨.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>P11a</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>모든 폰이 2칸씩 행동(이동 및 처치)할 수 있습니다.</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>모든 폰이 2칸씩 행동(이동 및 처치)할 수 있습니다. (중간 칸에 기물이 있으면 통과할 수 없습니다.)</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>중간 칸 통과 여부가 미정의. 폰은 도약 기물이 아니므로 통과 불가로 명확화.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>P11c</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>폰</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>폰이 꼭 반대편 끝이 아니더라도, 어느 한 방향의 끝에만 도달한다면 폰을 원하는 기물로 바꿀 수 있습니다.</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>폰이 꼭 반대편 끝이 아니더라도, 어느 한 방향의 끝(a·h파일 또는 1·8랭크)에 도달한다면 폰을 원하는 기물로 바꿀 수 있습니다.</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>'어느 한 방향의 끝'의 범위를 판의 4변으로 명확화.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>R1b</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>즉시, 룩의 가로와 세로 중 하나를 선택해 아군 룩을 제외한 그 줄에 있는 모든 기물을 제거합니다.</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>즉시, 룩의 가로와 세로 중 하나를 선택해 그 룩으로부터 4칸 이내에 있는 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>① 원안은 상대 킹이 그 줄에 있으면 1티어에 즉시 승리 → 킹 제외 필수. ② 1티어(첫 처치)에 판 한 줄 전멸은 과함 → 사거리 4칸 + 아군 포함으로 하향. 제거는 처치 카운트에 포함되지 않으므로 자기 진행도 늦추는 자연 페널티가 생김.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="66" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>R6a</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>다음 상대턴동안, 상대는 자신의 룩보다 위로 기물을 움직일 수 없습니다.</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>① 룩이 여럿/없을 때 기준이 미정의. ② 체크 상태에서 모든 합법수가 막히면 게임이 멈춤 → 체크 회피 예외.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="66" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>R6b</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>다음 상대턴동안, 상대는 자신의 룩보다 아래있는 기물을 움직일 수 없습니다.</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>R6a와 동일한 사유.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="66" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>R11b</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>게임 동안 한 번도 움직이지 않은 아군 기물을 선택하여 룩으로 만듭니다.</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>게임 동안 한 번도 움직이지 않은 아군 기물을 선택하여 룩으로 만듭니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>킹 변이 방지.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="66" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>R11c</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>룩</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>룩이 킹과 같은 가로열에 있다면 언제든지 캐슬링을 할 수 있습니다.</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>룩이 킹과 같은 가로열에 있다면 언제든지 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>'언제든지'의 범위를 명확화.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="66" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>N1c</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>방금 적을 처치한 나이트 한 칸 주변의 모든 기물을 제거합니다.</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>킹 제외 명시. 미명시 시 킹 인접 처치만으로 즉시 승리.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="66" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>N3a</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>다음 2회, 나이트의 상,하,좌,우 어느 한 방향에 폰이 있을경우, 그 폰과 나이트의 위치를 바꿉니다.</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>다음 2회, 나이트의 상·하·좌·우 어느 한 방향에 아군 폰이 있을 경우, 그 폰과 나이트의 위치를 바꿉니다.</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>'폰'이 아군/적군 중 무엇인지 미정의. 아군으로 명확화(적 폰이면 교환 정의와 충돌).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="66" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>N3b</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>다음 2턴동안, 서로 나이트만 쓸 수 있습니다.</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>다음 2턴 동안, 서로 나이트만 쓸 수 있습니다. (단, 체크 상태이거나 나이트가 없는 쪽은 일반적으로 움직일 수 있습니다.)</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>나이트가 없거나 나이트로 체크를 못 벗어나면 합법수가 0이 되어 게임이 멈춤 → 예외 추가.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="66" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>N3c</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>지정한 아군 나이트 좌우 1칸 모두 적 기물이 있고 나이트보다 기물점수가 높다면, 두 기물 중 기물점수가 낮은 기물로 변이됩니다.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>지정한 아군 나이트의 좌우 1칸 모두에 적 기물이 있고 둘 다 나이트보다 기물점수가 높다면, 나이트가 두 기물 중 기물점수가 낮은 기물로 변이됩니다.</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>변이 대상이 나이트 자신임을 명확화(원문은 주어가 모호).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="66" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>N6a</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>나이트가 밟고 간 나와 상대방의 기물을 2턴동안 포영상태로 만듭니다.</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>나이트가 밟고 간 나와 상대방의 기물을 2턴 동안 포영 상태로 만듭니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>킹 제외 명시. 나이트는 도약 기물이므로 '밟고 간'을 출발-도착 사이 L자 경로의 인접 칸으로 정의.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="66" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>N11b</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>나이트</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>나이트의 움직임 범위가 2배로 늘어나며 대각선으로 먼저 이동할 수 있습니다. (직선으로 두 번, 대각선으로 두 번)</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>나이트의 움직임 범위가 2배로 늘어나며 대각선으로 먼저 이동할 수 있습니다. (직선으로 두 칸 + 대각선으로 두 칸. 도약이므로 경로는 무시합니다.)</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>이동 형태를 좌표로 확정(기존 L자에 더해 (±2,±4)/(±4,±2) 형태 추가). 경로 무시 명시.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="66" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>B1a</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>(비밀) 다음 1회 4~5열에 내 폰과 상대 폰이 모두 있다면, 서로 교환합니다.</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 서로 교환합니다.</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>'열'을 랭크(가로줄)로 명확화.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="66" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>B1b</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>(비밀) 내 다음 2턴동안, 비숍이 움직이지 못합니다. 자신 주변 한 칸에 자신의 발판 색과 같은 기물이 온다면 제거합니다.</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>내 다음 2턴 동안, 비숍이 움직이지 못합니다. 그동안 비숍 주변 한 칸에 비숍이 서 있는 발판과 같은 색의 칸으로 적 기물이 온다면 그 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>'발판 색과 같은 기물'이 모호(기물 색인지 칸 색인지). 칸 색 기준 + 적 기물 한정 + 킹 제외로 확정.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>B3a</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>(비밀) 1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 홀수인경우, 폰 하나를 아군 빈 체스판에 소환합니다.</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 홀수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>'아군 빈 체스판'을 자기 진영 1~2랭크 빈칸으로 명확화. 또한 홀수(B3a)/짝수(B3b)는 한쪽이 반드시 참이므로 같은 드래프트에 동시 등장 금지 규칙 추가.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="66" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>B3b</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>(비밀) 1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 짝수인경우, 폰 하나를 아군 빈 체스판에 소환합니다.</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 짝수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>B3a와 동일한 사유.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="66" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>B6c</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>(비밀) 다음 1회, 비숍이 상대 기물을 처치시 그 기물 주위 한칸의 모든 기물을 제거합니다.</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>다음 1회, 비숍이 상대 기물을 처치 시 그 기물 주위 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>킹 제외 명시.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="66" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>B11c</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>(비밀) 지정한 상대 기물이 상대의 다음 2턴동안 처치나 제거되지 않는다면 상대의 지정된 기물의 강화 효과가 모두 사라집니다.</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않는다면, 그 기물이 받고 있던 강화 효과가 모두 사라집니다.</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>'그 기물의 강화'가 곧 '그 기물 종류의 강화 전부'인지 모호 → 지정 기물이 속한 기물 종류의 강화를 상대가 잃는 것으로 확정.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="66" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Q1a</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C25" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>아군 퀸이 체스판에서 대각선에 해당하는 칸에 도착할경우, 다음 턴에 그 위치중 비어있는 한 곳으로 이동할 수 있습니다.</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>아군 퀸이 판의 긴 대각선(a1-h8 / a8-h1)에 해당하는 칸에 도착할 경우, 다음 턴에 그 대각선 위의 비어있는 칸 한 곳으로 순간이동할 수 있습니다.</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>'대각선에 해당하는 칸'이 모호(모든 칸이 어떤 대각선엔 속함) → 두 개의 긴 대각선으로 확정.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="66" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Q1c</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C26" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>아군 퀸이 상대 퀸과 함께 제거됩니다.</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>아군 퀸이 상대 퀸과 함께 제거됩니다. (양쪽 퀸이 모두 살아있을 때만 선택 가능)</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>한쪽 퀸이 이미 없을 때의 처리가 미정의 → 선택 조건으로 명확화.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="66" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Q3a</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>모든 기물의 강화된 효과를 제거합니다.</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>자신과 상대가 지금까지 얻은 모든 강화 효과를 제거합니다. (이 강화 자신도 소멸하며, 이후 얻는 강화는 정상 적용됩니다.)</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>'모든 기물'이 양측인지 상대만인지 미정의 → 양측 전체 리셋으로 확정(자해 포함이라 자연 밸런스).</t>
         </is>
       </c>
     </row>
     <row r="28" ht="66" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Q6a</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>다음 상대턴동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다.</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>다음 상대턴 동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>킹 제외 명시.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="66" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Q11a</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C29" s="11" t="n">
+      <c r="C29" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>자신 주변 한 칸 내에 있는 모든 기물, 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함)</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>퀸 주변 한 칸 내에 있는 모든 기물, 그리고 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>킹 제외 명시. 킹 인접 시 즉시 승리 방지.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="66" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Q11b</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>아군 퀸이 2턴동안 포영상태가 되며 그동안, 포영된 위치에서 두 칸 이내에 상대 기물이 있을경우 그 기물을 제거합니다.</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>아군 퀸이 2턴 동안 포영 상태가 되며, 그동안 포영된 위치에서 두 칸 이내에 상대 기물이 있을 경우 그 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>킹 제외 명시.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="66" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Q11c</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>퀸</t>
         </is>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>퀸이 어디에 있든 킹 주변 한칸 이내 빈칸으로 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>퀸이 어디에 있든 아군 킹 주변 한 칸 이내의 빈칸으로 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>'킹'이 아군인지 상대인지 미정의 → 아군 킹으로 확정(귀환기 성격).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="66" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>K1d</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>K3a</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>[신규] 사용자 제안 - 킹 증강 철학 예시</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>이후 모든 강화에 필요한 처치 기물 수가 1 줄어듭니다. (1·3·6·11 → 0·2·5·10)</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>신규 추가. 킹 증강의 기준점이 되는 '진행 개입형' 증강.</t>
+      <c r="C32" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>나이트, 비숍 중 한 기물의 3번째 강화 효과를 선택해 강화합니다.</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>'3번째 강화'가 티어 순서(1→3→6→11 중 3번째 = 6개 티어)임을 명확화.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="66" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>K3a</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>K3c</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C33" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화 효과를 선택해 강화합니다.</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>'3번째 강화'가 티어 순서(1→3→6→11 중 3번째 = 6개 티어)임을 명확화.</t>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>룩, 퀸 중 한 기물의 6번째 강화 효과를 선택해 강화합니다.</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>원문 '6번째 강화'는 티어 표에 존재하지 않는 번호. 6개 티어를 뜻하면 K3a와 완전 중복되므로 11개 티어(4번째)로 확정해 상위 티어 선취 증강으로 차별화.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="66" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>K3c</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>K6b</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>룩, 퀸 중 한 기물의 6번째 강화 효과를 선택해 강화합니다.</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>원문 '6번째 강화'는 티어 표에 존재하지 않는 번호. 6개 티어를 뜻하면 K3a와 완전 중복되므로 11개 티어(4번째)로 확정해 상위 티어 선취 증강으로 차별화.</t>
+      <c r="C34" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>킹이 두 칸씩 움직일 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>원안은 킹 자체를 강화하는 효과라 '킹=플레이어' 철학과 어긋남. 사용자 신규 제안 #1(조건부 추가 강화)로 교체.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="66" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>K6b</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>K6c</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C35" s="11" t="n">
+      <c r="C35" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>킹이 두 칸씩 움직일 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>원안은 킹 자체를 강화하는 효과라 '킹=플레이어' 철학과 어긋남. 사용자 신규 제안 #1(조건부 추가 강화)로 교체.</t>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>킹이 퀸처럼 움직일 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>원안은 킹 직접 강화. 빗나간 선택을 되돌리는 '리스펙' 메타 증강으로 교체.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="66" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>K6c</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>K11b</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C36" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>킹이 퀸처럼 움직일 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>원안은 킹 직접 강화. 빗나간 선택을 되돌리는 '리스펙' 메타 증강으로 교체.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="66" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>K11b</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>킹</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="n">
+      <c r="C36" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>킹으로 3개의 기물을 더 처치하면 새로운 증강이 제시됩니다 (=이 게임에서 승리합니다)</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>원안은 ① 킹으로 직접 3킬이라는 사실상 달성 불가능한 조건이고 ② 킹 이동 강화를 뺀 개정안에서는 더욱 불가능. '킹을 포위한다'는 동일한 극적 승리 조건을 아군 기물 전체로 옮겨 달성 가능하게 재설계.</t>
         </is>
@@ -5260,107 +5178,107 @@
       </c>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="11" t="n"/>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>킹 보호</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>킹은 제거·포영·변이·교환·지정불가의 대상이 되지 않는다. 킹을 잃는 유일한 방법은 체크메이트다.</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>광역 제거/변이 증강(R1b, N1c, B6c, Q11a, Q11b, K11c 등)이 킹에 닿으면 1티어 증강만으로 즉시 승리가 나온다. 체스의 승리 조건 자체가 무너지므로 전역 예외가 반드시 필요하다.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>체크 회피 우선</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>이동을 제한하는 모든 효과(R6a/R6b/N3b 등)는 '체크에서 벗어나는 수'에는 적용되지 않는다. 이 예외를 적용해도 합법수가 없으면 그 턴은 자동으로 넘어간다.</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>제한 효과와 체크가 겹치면 합법수가 0이 되어 게임이 진행 불가 상태에 빠진다.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>제거 ≠ 처치</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>제거된 기물은 처치 카운트에 포함되지 않는다. (킹 증강 K1c로만 예외)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>원본 시트의 핵심 규칙. 광역 제거 증강의 자연스러운 브레이크 역할을 하므로 반드시 유지.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>드래프트 방식</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>처치 카운트가 1·3·6·11에 도달하면 해당 티어의 18개 증강 중 무작위 3개를 제시하고 1개를 고른다. K1b 보유 시 2개를 고른다. 이미 보유한 증강은 제시되지 않는다.</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>원본 시트는 기물×티어 격자만 있고 획득 방식이 없었다. 로그라이트 드래프트로 확정.</t>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>처치 카운트가 1·3·6·11에 도달하면, 그 처치를 해낸 기물의 칸(기물×티어)에 있는 선택지 3개를 그대로 펼쳐 그중 1개를 고른다. 폰이 승격하면서 잡았다면 승격 전 종류(폰)를 쓴다. K1b 를 갖고 있으면 드래프트를 한 번 더 돌린다. 이미 가진 증강과 지금 발동해도 아무 일이 없는 증강은 ✕ 로 잠겨 고를 수 없고, 칸 전체가 잠기면 고를 수 있는 다른 기물 칸으로 넘어간다.</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>원본 시트는 기물×티어 격자만 있고 획득 방식이 없었다. 칸마다 선택지가 정확히 3개라 '칸 하나를 그대로 펼치는' 방식으로 확정했다.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>상충 방지</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>B3a(홀수)/B3b(짝수)는 같은 드래프트에 동시에 제시되지 않는다.</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>한쪽이 반드시 참이므로 동시에 나오면 '무조건 맞는 쪽'이 정답이 되어 선택이 사라진다.</t>
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>동시 제시</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>B3a(홀수)/B3b(짝수)는 같은 칸에 있어 항상 함께 제시된다. 조건은 1턴 뒤에 판정하므로, 그 사이 기물점수가 바뀔 수 있어 선택은 여전히 도박이다.</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>칸을 통째로 펼치는 구조라 둘을 갈라놓을 수 없다. 대신 판정 시점이 미래라 '무조건 맞는 쪽'이 존재하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>비밀 증강</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>비밀 증강은 상대에게 표시되지 않으며, 한 번 발동한 뒤부터 공개된다. 2인 로컬(핫시트) 대전에서는 의미가 없으므로 AI전에서만 유효하다.</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>원본 시트 정의 유지 + 플레이 모드별 유효성 명시.</t>
         </is>
@@ -5397,95 +5315,95 @@
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="11" t="n"/>
+      <c r="A2" s="17" t="n"/>
+      <c r="B2" s="17" t="n"/>
     </row>
     <row r="3" ht="46" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>지정불가</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>나와 상대 둘 다 해당 기물을 움직일 수도, 처치 대상으로 삼을 수도 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>제거</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>특정 기물을 체스판에서 제거합니다. 이때 제거된 기물은 처치한 기물 수에 포함하지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>교환</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>내 기물과 상대 기물의 위치를 서로 바꿉니다. 바꿨을 때 어느 한쪽이라도 체크 상태가 되는 경우에는 바꿀 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>포영</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>해당 기물을 임시적으로 제거합니다. 기물이 있던 칸으로 다른 기물이 이동할 수 있습니다. 포영된 기물이 체스판으로 복귀할 때 그 위치에 다른 기물이 있다면 피아 상관없이 해당 기물을 제거합니다.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>비밀</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>상대방에게 자신이 고른 증강이 표시되지 않습니다. 단, 한 번 효과가 발동된 후에는 표시됩니다.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>변이</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>기물의 종류가 다른 종류로 바뀝니다. 색과 위치는 유지됩니다. 킹은 변이 대상이 아닙니다.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>처치</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>상대 기물을 정상적인 수로 잡는 것. 처치 카운트가 오르며 증강 해금의 기준이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>기물 점수</t>
         </is>
@@ -5522,7 +5440,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>처치 밸런스 (티어별 기물 강함 순)</t>
         </is>
@@ -5589,7 +5507,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>기물 밸런스 (기물별 티어 강함 순)</t>
         </is>
@@ -5680,7 +5598,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>통계상 자주 사용되는 기물</t>
         </is>
@@ -5884,14 +5802,14 @@
     <row r="45" ht="46" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>· → 대응 1: 킹 1개 티어에 K1d(필요 처치 수 -1)를 신설했다. 1개 티어에서 뽑으면 3·6·11이 2·5·10이 되어 11개 티어 도달률이 눈에 띄게 올라간다.</t>
+          <t>· → 한때 킹 1개 티어에 K1d(필요 처치 수 -1)를 신설했으나 되돌렸다. 칸마다 선택지가 정확히 3개라는 규칙이 드래프트 구조(칸 하나를 통째로 펼침)를 떠받치고 있어, 한 칸만 4개가 되면 그 칸에서만 규칙이 달라진다. 현재 24칸 전부 3개이며, 이 밸런스 문제는 아직 열려 있다.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="46" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>· → 대응 2(미적용, 검토 필요): 티어를 1·3·6·11 에서 1·3·6·9 로 낮추는 안. 한 판 평균 처치 수가 양측 합산 10.7 이라 11은 사실상 '한 진영이 판을 압도했을 때'만 열린다.</t>
+          <t>· → 대응(미적용, 검토 필요): 티어를 1·3·6·11 에서 1·3·6·9 로 낮추는 안. 한 판 평균 처치 수가 양측 합산 10.7 이라 11은 사실상 '한 진영이 판을 압도했을 때'만 열린다.</t>
         </is>
       </c>
     </row>

--- a/docs/무제체스_증강표_v2.xlsx
+++ b/docs/무제체스_증강표_v2.xlsx
@@ -882,9 +882,9 @@
           <t>[B1c] (비밀) 다음 상대의 2턴 동안 지정한 상대 폰이 한 번도 움직이지 않았을 경우, 그 폰을 제거합니다.</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>[B3c] (비밀) 적을 처치한 비숍이 1턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>[B3c] (비밀) 적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -2821,45 +2821,49 @@
       </c>
     </row>
     <row r="44" ht="48" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>B3c</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>비숍</t>
         </is>
       </c>
-      <c r="C44" s="17" t="n">
+      <c r="C44" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>영구지속</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>적을 처치한 비숍이 1턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>(동일)</t>
-        </is>
-      </c>
-      <c r="H44" s="17" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>(비밀) 방금 적을 처치한 비숍이 1턴동안 살아있을경우, 자신의 처치된 기물 중 하나를 스폰위치에 소환합니다. (다른 기물이 있을경우 불가)</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>대상지정</t>
         </is>
       </c>
-      <c r="I44" s="17" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>개정</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
@@ -4063,7 +4067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4717,7 +4721,7 @@
     <row r="23" ht="66" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>B6c</t>
+          <t>B3c</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
@@ -4726,28 +4730,28 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>(비밀) 다음 1회, 비숍이 상대 기물을 처치시 그 기물 주위 한칸의 모든 기물을 제거합니다.</t>
+          <t>(비밀) 방금 적을 처치한 비숍이 1턴동안 살아있을경우, 자신의 처치된 기물 중 하나를 스폰위치에 소환합니다. (다른 기물이 있을경우 불가)</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>다음 1회, 비숍이 상대 기물을 처치 시 그 기물 주위 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
+          <t>적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>킹 제외 명시.</t>
+          <t>살아남아야 하는 기간을 1턴 → 2턴으로. 한 턴은 너무 쉽게 통과해 조건이 없는 것과 같았다.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="66" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>B11c</t>
+          <t>B6c</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
@@ -4756,58 +4760,58 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>(비밀) 지정한 상대 기물이 상대의 다음 2턴동안 처치나 제거되지 않는다면 상대의 지정된 기물의 강화 효과가 모두 사라집니다.</t>
+          <t>(비밀) 다음 1회, 비숍이 상대 기물을 처치시 그 기물 주위 한칸의 모든 기물을 제거합니다.</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않는다면, 그 기물이 받고 있던 강화 효과가 모두 사라집니다.</t>
+          <t>다음 1회, 비숍이 상대 기물을 처치 시 그 기물 주위 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>'그 기물의 강화'가 곧 '그 기물 종류의 강화 전부'인지 모호 → 지정 기물이 속한 기물 종류의 강화를 상대가 잃는 것으로 확정.</t>
+          <t>킹 제외 명시.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="66" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>Q1a</t>
+          <t>B11c</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>퀸</t>
+          <t>비숍</t>
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 체스판에서 대각선에 해당하는 칸에 도착할경우, 다음 턴에 그 위치중 비어있는 한 곳으로 이동할 수 있습니다.</t>
+          <t>(비밀) 지정한 상대 기물이 상대의 다음 2턴동안 처치나 제거되지 않는다면 상대의 지정된 기물의 강화 효과가 모두 사라집니다.</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 판의 긴 대각선(a1-h8 / a8-h1)에 해당하는 칸에 도착할 경우, 다음 턴에 그 대각선 위의 비어있는 칸 한 곳으로 순간이동할 수 있습니다.</t>
+          <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않는다면, 그 기물이 받고 있던 강화 효과가 모두 사라집니다.</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>'대각선에 해당하는 칸'이 모호(모든 칸이 어떤 대각선엔 속함) → 두 개의 긴 대각선으로 확정.</t>
+          <t>'그 기물의 강화'가 곧 '그 기물 종류의 강화 전부'인지 모호 → 지정 기물이 속한 기물 종류의 강화를 상대가 잃는 것으로 확정.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="66" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>Q1c</t>
+          <t>Q1a</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
@@ -4820,24 +4824,24 @@
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 상대 퀸과 함께 제거됩니다.</t>
+          <t>아군 퀸이 체스판에서 대각선에 해당하는 칸에 도착할경우, 다음 턴에 그 위치중 비어있는 한 곳으로 이동할 수 있습니다.</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 상대 퀸과 함께 제거됩니다. (양쪽 퀸이 모두 살아있을 때만 선택 가능)</t>
+          <t>아군 퀸이 판의 긴 대각선(a1-h8 / a8-h1)에 해당하는 칸에 도착할 경우, 다음 턴에 그 대각선 위의 비어있는 칸 한 곳으로 순간이동할 수 있습니다.</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>한쪽 퀸이 이미 없을 때의 처리가 미정의 → 선택 조건으로 명확화.</t>
+          <t>'대각선에 해당하는 칸'이 모호(모든 칸이 어떤 대각선엔 속함) → 두 개의 긴 대각선으로 확정.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="66" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>Q3a</t>
+          <t>Q1c</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
@@ -4846,28 +4850,28 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>모든 기물의 강화된 효과를 제거합니다.</t>
+          <t>아군 퀸이 상대 퀸과 함께 제거됩니다.</t>
         </is>
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>자신과 상대가 지금까지 얻은 모든 강화 효과를 제거합니다. (이 강화 자신도 소멸하며, 이후 얻는 강화는 정상 적용됩니다.)</t>
+          <t>아군 퀸이 상대 퀸과 함께 제거됩니다. (양쪽 퀸이 모두 살아있을 때만 선택 가능)</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>'모든 기물'이 양측인지 상대만인지 미정의 → 양측 전체 리셋으로 확정(자해 포함이라 자연 밸런스).</t>
+          <t>한쪽 퀸이 이미 없을 때의 처리가 미정의 → 선택 조건으로 명확화.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="66" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>Q6a</t>
+          <t>Q3a</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
@@ -4876,28 +4880,28 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>다음 상대턴동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다.</t>
+          <t>모든 기물의 강화된 효과를 제거합니다.</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다. (킹 제외)</t>
+          <t>자신과 상대가 지금까지 얻은 모든 강화 효과를 제거합니다. (이 강화 자신도 소멸하며, 이후 얻는 강화는 정상 적용됩니다.)</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>킹 제외 명시.</t>
+          <t>'모든 기물'이 양측인지 상대만인지 미정의 → 양측 전체 리셋으로 확정(자해 포함이라 자연 밸런스).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="66" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>Q11a</t>
+          <t>Q6a</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
@@ -4906,28 +4910,28 @@
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>자신 주변 한 칸 내에 있는 모든 기물, 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함)</t>
+          <t>다음 상대턴동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다.</t>
         </is>
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>퀸 주변 한 칸 내에 있는 모든 기물, 그리고 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
+          <t>다음 상대턴 동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
         <is>
-          <t>킹 제외 명시. 킹 인접 시 즉시 승리 방지.</t>
+          <t>킹 제외 명시.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="66" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>Q11b</t>
+          <t>Q11a</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
@@ -4940,24 +4944,24 @@
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 2턴동안 포영상태가 되며 그동안, 포영된 위치에서 두 칸 이내에 상대 기물이 있을경우 그 기물을 제거합니다.</t>
+          <t>자신 주변 한 칸 내에 있는 모든 기물, 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함)</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 2턴 동안 포영 상태가 되며, 그동안 포영된 위치에서 두 칸 이내에 상대 기물이 있을 경우 그 기물을 제거합니다. (킹 제외)</t>
+          <t>퀸 주변 한 칸 내에 있는 모든 기물, 그리고 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>킹 제외 명시.</t>
+          <t>킹 제외 명시. 킹 인접 시 즉시 승리 방지.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="66" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>Q11c</t>
+          <t>Q11b</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
@@ -4970,54 +4974,54 @@
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>퀸이 어디에 있든 킹 주변 한칸 이내 빈칸으로 움직일 수 있습니다.</t>
+          <t>아군 퀸이 2턴동안 포영상태가 되며 그동안, 포영된 위치에서 두 칸 이내에 상대 기물이 있을경우 그 기물을 제거합니다.</t>
         </is>
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>퀸이 어디에 있든 아군 킹 주변 한 칸 이내의 빈칸으로 움직일 수 있습니다.</t>
+          <t>아군 퀸이 2턴 동안 포영 상태가 되며, 그동안 포영된 위치에서 두 칸 이내에 상대 기물이 있을 경우 그 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
-          <t>'킹'이 아군인지 상대인지 미정의 → 아군 킹으로 확정(귀환기 성격).</t>
+          <t>킹 제외 명시.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="66" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>K3a</t>
+          <t>Q11c</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>킹</t>
+          <t>퀸</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화 효과를 선택해 강화합니다.</t>
+          <t>퀸이 어디에 있든 킹 주변 한칸 이내 빈칸으로 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>퀸이 어디에 있든 아군 킹 주변 한 칸 이내의 빈칸으로 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>'3번째 강화'가 티어 순서(1→3→6→11 중 3번째 = 6개 티어)임을 명확화.</t>
+          <t>'킹'이 아군인지 상대인지 미정의 → 아군 킹으로 확정(귀환기 성격).</t>
         </is>
       </c>
     </row>
     <row r="33" ht="66" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>K3c</t>
+          <t>K3a</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
@@ -5030,24 +5034,24 @@
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>룩, 퀸 중 한 기물의 6번째 강화 효과를 선택해 강화합니다.</t>
+          <t>나이트, 비숍 중 한 기물의 3번째 강화 효과를 선택해 강화합니다.</t>
         </is>
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>원문 '6번째 강화'는 티어 표에 존재하지 않는 번호. 6개 티어를 뜻하면 K3a와 완전 중복되므로 11개 티어(4번째)로 확정해 상위 티어 선취 증강으로 차별화.</t>
+          <t>'3번째 강화'가 티어 순서(1→3→6→11 중 3번째 = 6개 티어)임을 명확화.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="66" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>K6b</t>
+          <t>K3c</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
@@ -5056,28 +5060,28 @@
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>킹이 두 칸씩 움직일 수 있습니다.</t>
+          <t>룩, 퀸 중 한 기물의 6번째 강화 효과를 선택해 강화합니다.</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
+          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>원안은 킹 자체를 강화하는 효과라 '킹=플레이어' 철학과 어긋남. 사용자 신규 제안 #1(조건부 추가 강화)로 교체.</t>
+          <t>원문 '6번째 강화'는 티어 표에 존재하지 않는 번호. 6개 티어를 뜻하면 K3a와 완전 중복되므로 11개 티어(4번째)로 확정해 상위 티어 선취 증강으로 차별화.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="66" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>K6c</t>
+          <t>K6b</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
@@ -5090,45 +5094,75 @@
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>킹이 퀸처럼 움직일 수 있습니다.</t>
+          <t>킹이 두 칸씩 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
+          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>원안은 킹 직접 강화. 빗나간 선택을 되돌리는 '리스펙' 메타 증강으로 교체.</t>
+          <t>원안은 킹 자체를 강화하는 효과라 '킹=플레이어' 철학과 어긋남. 사용자 신규 제안 #1(조건부 추가 강화)로 교체.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="66" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
+          <t>K6c</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>킹</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>킹이 퀸처럼 움직일 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>원안은 킹 직접 강화. 빗나간 선택을 되돌리는 '리스펙' 메타 증강으로 교체.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="66" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
           <t>K11b</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>킹</t>
         </is>
       </c>
-      <c r="C36" s="17" t="n">
+      <c r="C37" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>킹으로 3개의 기물을 더 처치하면 새로운 증강이 제시됩니다 (=이 게임에서 승리합니다)</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>원안은 ① 킹으로 직접 3킬이라는 사실상 달성 불가능한 조건이고 ② 킹 이동 강화를 뺀 개정안에서는 더욱 불가능. '킹을 포위한다'는 동일한 극적 승리 조건을 아군 기물 전체로 옮겨 달성 가능하게 재설계.</t>
         </is>

--- a/docs/무제체스_증강표_v2.xlsx
+++ b/docs/무제체스_증강표_v2.xlsx
@@ -806,7 +806,7 @@
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>[N1c] 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
+          <t>[N1c] 다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -2221,13 +2221,13 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>영구지속</t>
+          <t>횟수제한</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
+          <t>다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
+          <t>다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>킹 제외 명시. 미명시 시 킹 인접 처치만으로 즉시 승리.</t>
+          <t>킹 제외 명시. 영구지속 → 다음 1회. 이 증강을 열어 준 처치에는 발동하지 않는다 — 1처치에 즉시 광역 제거는 첫 티어치고 너무 셌다.</t>
         </is>
       </c>
     </row>

--- a/docs/무제체스_증강표_v2.xlsx
+++ b/docs/무제체스_증강표_v2.xlsx
@@ -614,12 +614,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>[P1a] 다음 상대턴 동안, 지정한 자신의 폰 하나가 지정불가 상태가 됩니다.</t>
+          <t>[P1a] 다음 상대턴 동안, 지정한 아군 폰 하나가 지정불가 상태가 됩니다.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>[P3a] 내 다음 2턴 동안, 폰으로 다른 기물을 처치할 시 처치 카운팅이 2배로 적용됩니다.</t>
+          <t>[P3a] 내 다음 2턴 동안, 폰으로 적을 처치하면 처치 수가 2배로 쌓입니다.</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>[P11a] 모든 폰이 2칸씩 행동(이동 및 처치)할 수 있습니다. (중간 칸에 기물이 있으면 통과할 수 없습니다.)</t>
+          <t>[P11a] 모든 폰이 한 번에 두 칸까지 움직이고 처치할 수 있습니다. (지나갈 칸에 기물이 있으면 통과하지 못합니다.)</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>[P1b] 다음 1회, 폰이 두 번 전진할 수 있습니다. (전진할 곳에 다른 기물이 있을 시 움직일 수 없습니다.)</t>
+          <t>[P1b] 다음 1회, 폰이 두 칸 전진할 수 있습니다. (지나갈 칸과 도착할 칸이 모두 비어 있어야 합니다.)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>[P6b] 폰이 정면에 있는 적 기물도 처치할 수 있습니다.</t>
+          <t>[P6b] 폰이 바로 앞에 있는 적 기물도 처치할 수 있습니다.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>[P11b] 내 다음 3턴 동안, 지정한 폰을 퀸으로 변경합니다. 3턴 후, 그 폰은 제거됩니다.</t>
+          <t>[P11b] 지정한 아군 폰이 내 다음 3턴 동안 퀸이 됩니다. 3턴이 지나면 그 기물은 제거됩니다.</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>[P1c] 적을 처치한 폰이 다음 상대턴 동안, 가장 가까운 상대 폰과 함께 포영됩니다.</t>
+          <t>[P1c] 폰이 적을 처치하면, 그 폰과 가장 가까운 상대 폰이 다음 상대턴 동안 함께 포영됩니다.</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>[P3c] 폰이 적 기물을 처치한 후 원래 자리로 돌아올 수 있습니다. (선택 사항)</t>
+          <t>[P3c] 폰이 적을 처치한 뒤 원래 자리로 되돌아올 수 있습니다. (고르지 않아도 됩니다.)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>[P6c] 적을 처치한 폰의 전방 2칸 이내에 적 기물이 있을 시 교환합니다. 이때 상대 기물의 기물점수가 더 높다면 그 기물을 폰으로 변이시킵니다. (킹 제외)</t>
+          <t>[P6c] 폰이 적을 처치하면, 그 폰 앞 2칸 이내에 있는 적 기물 하나와 위치를 교환합니다. 그 기물의 점수가 폰보다 높다면 폰으로 변이시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>[P11c] 폰이 꼭 반대편 끝이 아니더라도, 어느 한 방향의 끝(a·h파일 또는 1·8랭크)에 도달한다면 폰을 원하는 기물로 바꿀 수 있습니다.</t>
+          <t>[P11c] 폰이 반대편 끝이 아니어도, 판의 어느 한쪽 끝(a·h파일 또는 1·8랭크)에 닿으면 원하는 기물로 바꿀 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>[R3a] 다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치하지는 못합니다.)</t>
+          <t>[R3a] 다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치할 수는 없습니다.)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>[R6a] 다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
+          <t>[R6a] 다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -710,22 +710,22 @@
       <c r="A9" s="7" t="n"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>[R1b] 즉시, 룩의 가로와 세로 중 하나를 선택해 그 룩으로부터 4칸 이내에 있는 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
+          <t>[R1b] 즉시, 룩이 선 가로줄과 세로줄 중 하나를 골라 그 룩에서 4칸 이내의 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>[R3b] 다음 2턴 동안, 룩이 처치한 기물과 동일한 종류의 상대 기물을 모두 포영 상태로 만듭니다.</t>
+          <t>[R3b] 룩이 적을 처치하면, 그 기물과 같은 종류의 상대 기물이 모두 2턴 동안 포영됩니다.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>[R6b] 다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
+          <t>[R6b] 다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>[R11b] 게임 동안 한 번도 움직이지 않은 아군 기물을 선택하여 룩으로 만듭니다. (킹 제외)</t>
+          <t>[R11b] 게임 내내 한 번도 움직이지 않은 아군 기물 하나를 골라 룩으로 만듭니다. (킹 제외)</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>[R1c] 내 다음 2턴 동안, 적을 처치한 룩과 지정한 상대 기물 하나가 지정불가 상태가 됩니다.</t>
+          <t>[R1c] 룩이 적을 처치하면, 그 룩과 지정한 상대 기물 하나가 내 다음 2턴 동안 지정불가 상태가 됩니다.</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>[R6c] 지정한 아군 룩과 상대 폰의 위치를 교환합니다.</t>
+          <t>[R6c] 지정한 아군 룩과 지정한 상대 폰의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>[R11c] 룩이 킹과 같은 가로열에 있다면 언제든지 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
+          <t>[R11c] 룩이 킹과 같은 가로줄에 있다면 언제든 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>[N3a] 다음 2회, 나이트의 상·하·좌·우 어느 한 방향에 아군 폰이 있을 경우, 그 폰과 나이트의 위치를 바꿉니다.</t>
+          <t>[N3a] 다음 2회, 나이트의 상·하·좌·우 중 한 방향에 아군 폰이 있으면 그 폰과 나이트의 위치를 바꿉니다.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>[N6a] 나이트가 밟고 간 나와 상대방의 기물을 2턴 동안 포영 상태로 만듭니다. (킹 제외)</t>
+          <t>[N6a] 나이트가 지나간 칸에 있던 기물을 피아 구분 없이 2턴 동안 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>[N11a] 나이트를 2회 이상 강화한 상태라면, 비어있는 칸에 1턴 동안 지정불가 상태인 나이트를 2개 소환합니다.</t>
+          <t>[N11a] 나이트 증강을 2개 이상 가지고 있다면, 빈칸에 나이트 2개를 소환합니다. 소환된 나이트는 1턴 동안 지정불가입니다.</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>[N1b] 적을 처치한 나이트와 자신의 비숍 중 하나의 위치를 교환합니다.</t>
+          <t>[N1b] 나이트가 적을 처치할 때마다, 그 나이트와 아군 비숍 하나의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>[N3b] 다음 2턴 동안, 서로 나이트만 쓸 수 있습니다. (단, 체크 상태이거나 나이트가 없는 쪽은 일반적으로 움직일 수 있습니다.)</t>
+          <t>[N3b] 다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>[N6b] 상대 나이트와 내 나이트의 위치가 가로·세로 모두 5칸 이상 차이날 경우, 상대 나이트를 처치합니다. (대상이 여러 개일 경우 자신이 선택)</t>
+          <t>[N6b] 상대 나이트가 내 나이트와 가로·세로 모두 5칸 이상 떨어져 있다면 그 나이트를 처치합니다. (대상이 여럿이면 내가 고릅니다.)</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -806,22 +806,22 @@
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>[N1c] 다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
+          <t>[N1c] 다음 1회, 나이트가 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>[N3c] 지정한 아군 나이트의 좌우 1칸 모두에 적 기물이 있고 둘 다 나이트보다 기물점수가 높다면, 나이트가 두 기물 중 기물점수가 낮은 기물로 변이됩니다.</t>
+          <t>[N3c] 지정한 아군 나이트의 좌우 한 칸에 모두 적 기물이 있고 둘 다 나이트보다 점수가 높다면, 나이트가 둘 중 점수가 낮은 기물로 변이합니다.</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>[N6c] 즉시, 나이트가 킹과 퀸을 제외한 상대의 가장 낮은 점수의 기물을 하나 없애고 그 위치로 이동합니다. (여러 개일 시 자신이 선택)</t>
+          <t>[N6c] 즉시, 나이트가 상대의 가장 낮은 점수 기물 하나를 없애고 그 자리로 이동합니다. (킹·퀸 제외. 대상이 여럿이면 내가 고릅니다.)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>[N11c] 자신의 나이트가 살아있고 상대의 퀸이 살아있다면, 두 기물 모두 제거합니다.</t>
+          <t>[N11c] 아군 나이트와 상대 퀸이 모두 살아 있다면, 둘 다 제거합니다.</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>[B1a] (비밀) 다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 서로 교환합니다.</t>
+          <t>[B1a] (비밀) 다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 두 폰의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>[B3a] (비밀) 1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 홀수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
+          <t>[B3a] (비밀) 1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 홀수라면 아군 진영 빈칸에 폰 하나를 소환합니다.</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>[B6a] (비밀) 상대의 다음 2턴 동안, 비숍이 처치당할 경우 비숍을 처치한 상대 기물도 같이 죽습니다. (킹·퀸 제외)</t>
+          <t>[B6a] (비밀) 상대의 다음 2턴 동안, 비숍이 처치당하면 그 비숍을 처치한 상대 기물도 함께 제거됩니다. (킹·퀸 제외)</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>[B11a] (비밀) 다음 1회 아군 킹이 체크를 당할 때, 체크를 한 기물을 1턴 동안 지정불가 상태로 만듭니다.</t>
+          <t>[B11a] (비밀) 다음 1회, 아군 킹이 체크를 당하면 체크를 건 기물을 1턴 동안 지정불가 상태로 만듭니다.</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       <c r="A15" s="7" t="n"/>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>[B1b] (비밀) 내 다음 2턴 동안, 비숍이 움직이지 못합니다. 그동안 비숍 주변 한 칸에 비숍이 서 있는 발판과 같은 색의 칸으로 적 기물이 온다면 그 기물을 제거합니다. (킹 제외)</t>
+          <t>[B1b] (비밀) 내 다음 2턴 동안 비숍이 움직이지 못합니다. 그동안 비숍에 인접한 칸 중 비숍이 선 칸과 같은 색인 칸으로 적 기물이 오면 그 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>[B3b] (비밀) 1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 짝수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
+          <t>[B3b] (비밀) 1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 짝수라면 아군 진영 빈칸에 폰 하나를 소환합니다.</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>[B6b] (비밀) 상대의 다음 1턴 동안, 지정한 상대 기물이 움직이지 않는다면 제거됩니다. (킹·퀸 제외)</t>
+          <t>[B6b] (비밀) 상대의 다음 1턴 동안 지정한 상대 기물이 움직이지 않으면, 그 기물을 제거합니다. (킹·퀸 제외)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>[B11b] (비밀) 아군 퀸이 죽은 상태라면 내 다음 3턴 동안, 비숍이 퀸처럼 움직일 수 있습니다.</t>
+          <t>[B11b] (비밀) 아군 퀸이 잡힌 상태라면, 내 다음 3턴 동안 비숍이 퀸처럼 움직일 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -879,22 +879,22 @@
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>[B1c] (비밀) 다음 상대의 2턴 동안 지정한 상대 폰이 한 번도 움직이지 않았을 경우, 그 폰을 제거합니다.</t>
+          <t>[B1c] (비밀) 지정한 상대 폰이 상대의 다음 2턴 동안 한 번도 움직이지 않으면, 그 폰을 제거합니다.</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>[B3c] (비밀) 적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
+          <t>[B3c] (비밀) 비숍이 적을 처치하고 2턴을 살아남으면, 잃었던 아군 기물 하나를 그 기물의 시작 칸에 되살립니다. (그 칸이 비어 있어야 합니다.)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>[B6c] (비밀) 다음 1회, 비숍이 상대 기물을 처치 시 그 기물 주위 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
+          <t>[B6c] (비밀) 다음 1회, 비숍이 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>[B11c] (비밀) 지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않는다면, 그 기물이 받고 있던 강화 효과가 모두 사라집니다.</t>
+          <t>[B11c] (비밀) 지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않으면, 그 기물이 받고 있던 증강 효과가 모두 사라집니다.</t>
         </is>
       </c>
     </row>
@@ -906,22 +906,22 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>[Q1a] 아군 퀸이 판의 긴 대각선(a1-h8 / a8-h1)에 해당하는 칸에 도착할 경우, 다음 턴에 그 대각선 위의 비어있는 칸 한 곳으로 순간이동할 수 있습니다.</t>
+          <t>[Q1a] 아군 퀸이 판의 긴 대각선(a1–h8 / a8–h1) 칸에 도착하면, 다음 턴에 그 대각선 위의 빈칸 한 곳으로 순간이동할 수 있습니다.</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>[Q3a] 자신과 상대가 지금까지 얻은 모든 강화 효과를 제거합니다. (이 강화 자신도 소멸하며, 이후 얻는 강화는 정상 적용됩니다.)</t>
+          <t>[Q3a] 나와 상대가 지금까지 얻은 증강 효과를 모두 제거합니다. (이 증강도 함께 사라지며, 이후 얻는 증강은 정상 적용됩니다.)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>[Q6a] 다음 상대턴 동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다. (킹 제외)</t>
+          <t>[Q6a] 다음 상대턴 동안, 아군 퀸과 지정한 기물 하나를 함께 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>[Q11a] 퀸 주변 한 칸 내에 있는 모든 기물, 그리고 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
+          <t>[Q11a] 퀸 주변 한 칸의 모든 기물과, 그 기물들과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
         </is>
       </c>
     </row>
@@ -929,22 +929,22 @@
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>[Q1b] 내 다음 5턴 동안, 퀸이 상대 퀸과 함께 지정불가 상태가 됩니다.</t>
+          <t>[Q1b] 내 다음 5턴 동안, 아군 퀸과 상대 퀸이 함께 지정불가 상태가 됩니다.</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>[Q3b] 다음 1회, 다음 상대턴 동안 아군 퀸을 포영 상태로 만듭니다.</t>
+          <t>[Q3b] 1회에 한해, 다음 상대턴 동안 아군 퀸을 포영시킵니다.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>[Q6b] 퀸을 1회 이상 강화한 상태라면, 퀸이 나이트처럼도 움직일 수 있습니다.</t>
+          <t>[Q6b] 퀸 증강을 1개 이상 가지고 있다면, 퀸이 나이트처럼도 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>[Q11b] 아군 퀸이 2턴 동안 포영 상태가 되며, 그동안 포영된 위치에서 두 칸 이내에 상대 기물이 있을 경우 그 기물을 제거합니다. (킹 제외)</t>
+          <t>[Q11b] 아군 퀸이 2턴 동안 포영되며, 그동안 포영된 자리에서 두 칸 이내에 들어온 상대 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
     </row>
@@ -952,22 +952,22 @@
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>[Q1c] 아군 퀸이 상대 퀸과 함께 제거됩니다. (양쪽 퀸이 모두 살아있을 때만 선택 가능)</t>
+          <t>[Q1c] 아군 퀸과 상대 퀸을 함께 제거합니다. (양쪽 퀸이 모두 살아 있을 때만 고를 수 있습니다.)</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>[Q3c] 이 게임에서 아군 퀸을 상대방이 처치해도 상대의 처치 카운트에 더해지지 않습니다.</t>
+          <t>[Q3c] 이 판에서 아군 퀸이 처치당해도 상대의 처치 수에 더해지지 않습니다.</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>[Q6c] 아군 퀸이 킹을 제외한 상대의 가장 높은 점수의 기물과 위치가 교환됩니다.</t>
+          <t>[Q6c] 아군 퀸과, 킹을 제외한 상대의 가장 높은 점수 기물의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>[Q11c] 퀸이 어디에 있든 아군 킹 주변 한 칸 이내의 빈칸으로 움직일 수 있습니다.</t>
+          <t>[Q11c] 퀸이 어디에 있든 아군 킹 주변 한 칸의 빈칸으로 움직일 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -979,22 +979,22 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>[K1a] 다음 1회, 킹이 체크를 당한 경우 퀸과 킹의 위치를 바꿀 수 있습니다.</t>
+          <t>[K1a] 다음 1회, 킹이 체크를 당하면 퀸과 킹의 위치를 바꿀 수 있습니다.</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>[K3a] 나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>[K3a] 나이트·비숍 중 한 기물의 6개 티어 증강 하나를 골라 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>[K6a] 다음 1회, 다른 기물과 함께 킹을 한 번 움직일 수 있습니다.</t>
+          <t>[K6a] 다음 1회, 다른 기물을 움직인 뒤 킹도 한 번 더 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>[K11a] 킹이 아군 폰 하나를 상하로 지정한 위치까지 이동시킵니다. (기물을 넘어서는 갈 수 없습니다.)</t>
+          <t>[K11a] 킹이 아군 폰 하나를 위아래 방향으로 지정한 칸까지 옮깁니다. (다른 기물을 넘어갈 수는 없습니다.)</t>
         </is>
       </c>
     </row>
@@ -1002,22 +1002,22 @@
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>[K1b] 자신의 다음 강화에서 선택지를 두 개 고를 수 있습니다.</t>
+          <t>[K1b] 다음 증강을 고를 때 선택지를 두 개 고를 수 있습니다.</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>[K3b] 상대 기물과 내 기물의 점수 차이만큼, 원하는 기물을 킹의 상하좌우에 배치할 수 있습니다. (상하좌우에 다른 기물이 있다면 그 칸에는 배치 불가)</t>
+          <t>[K3b] 상대와 나의 기물 점수 차이만큼 예산을 받아, 그만큼 원하는 기물을 킹의 상하좌우 빈칸에 배치합니다. (폰 1 · 나이트 3 · 비숍 3 · 룩 5 · 퀸 9점. 이미 기물이 있는 칸에는 배치할 수 없습니다.)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>[K6b] 지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
+          <t>[K6b] 같은 기물의 증강을 2개 이상 가지고 있다면, 그 기물의 1개 티어 증강 하나를 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>[K11b] 이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
+          <t>[K11b] 이 증강을 얻은 뒤부터, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 차지하면 즉시 승리합니다.</t>
         </is>
       </c>
     </row>
@@ -1025,22 +1025,22 @@
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>[K1c] 자신의 모든 제거를 처치로 간주합니다.</t>
+          <t>[K1c] 내가 일으킨 제거를 모두 처치로 셉니다.</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>[K3c] 룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>[K3c] 룩·퀸 중 한 기물의 11개 티어 증강 하나를 골라 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>[K6c] 이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
+          <t>[K6c] 이미 가진 증강 하나를 골라, 같은 기물·같은 티어의 다른 증강으로 바꿉니다.</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>[K11c] 서로의 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
+          <t>[K11c] 양쪽 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="E3" s="17" t="inlineStr"/>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 지정한 자신의 폰 하나가 지정불가 상태가 됩니다.</t>
+          <t>다음 상대턴 동안, 지정한 아군 폰 하나가 지정불가 상태가 됩니다.</t>
         </is>
       </c>
       <c r="G3" s="17" t="inlineStr">
@@ -1262,7 +1262,7 @@
       <c r="E4" s="17" t="inlineStr"/>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>다음 1회, 폰이 두 번 전진할 수 있습니다. (전진할 곳에 다른 기물이 있을 시 움직일 수 없습니다.)</t>
+          <t>다음 1회, 폰이 두 칸 전진할 수 있습니다. (지나갈 칸과 도착할 칸이 모두 비어 있어야 합니다.)</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
@@ -1299,7 +1299,7 @@
       <c r="E5" s="17" t="inlineStr"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>적을 처치한 폰이 다음 상대턴 동안, 가장 가까운 상대 폰과 함께 포영됩니다.</t>
+          <t>폰이 적을 처치하면, 그 폰과 가장 가까운 상대 폰이 다음 상대턴 동안 함께 포영됩니다.</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -1336,7 +1336,7 @@
       <c r="E6" s="17" t="inlineStr"/>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>내 다음 2턴 동안, 폰으로 다른 기물을 처치할 시 처치 카운팅이 2배로 적용됩니다.</t>
+          <t>내 다음 2턴 동안, 폰으로 적을 처치하면 처치 수가 2배로 쌓입니다.</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -1414,7 +1414,7 @@
       <c r="E8" s="17" t="inlineStr"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>폰이 적 기물을 처치한 후 원래 자리로 돌아올 수 있습니다. (선택 사항)</t>
+          <t>폰이 적을 처치한 뒤 원래 자리로 되돌아올 수 있습니다. (고르지 않아도 됩니다.)</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="E10" s="17" t="inlineStr"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>폰이 정면에 있는 적 기물도 처치할 수 있습니다.</t>
+          <t>폰이 바로 앞에 있는 적 기물도 처치할 수 있습니다.</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>적을 처치한 폰의 전방 2칸 이내에 적 기물이 있을 시 교환합니다. 이때 상대 기물의 기물점수가 더 높다면 그 기물을 폰으로 변이시킵니다. (킹 제외)</t>
+          <t>폰이 적을 처치하면, 그 폰 앞 2칸 이내에 있는 적 기물 하나와 위치를 교환합니다. 그 기물의 점수가 폰보다 높다면 폰으로 변이시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1570,7 +1570,7 @@
       <c r="E12" s="6" t="inlineStr"/>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>모든 폰이 2칸씩 행동(이동 및 처치)할 수 있습니다. (중간 칸에 기물이 있으면 통과할 수 없습니다.)</t>
+          <t>모든 폰이 한 번에 두 칸까지 움직이고 처치할 수 있습니다. (지나갈 칸에 기물이 있으면 통과하지 못합니다.)</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1611,7 +1611,7 @@
       <c r="E13" s="17" t="inlineStr"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>내 다음 3턴 동안, 지정한 폰을 퀸으로 변경합니다. 3턴 후, 그 폰은 제거됩니다.</t>
+          <t>지정한 아군 폰이 내 다음 3턴 동안 퀸이 됩니다. 3턴이 지나면 그 기물은 제거됩니다.</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -1648,7 +1648,7 @@
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>폰이 꼭 반대편 끝이 아니더라도, 어느 한 방향의 끝(a·h파일 또는 1·8랭크)에 도달한다면 폰을 원하는 기물로 바꿀 수 있습니다.</t>
+          <t>폰이 반대편 끝이 아니어도, 판의 어느 한쪽 끝(a·h파일 또는 1·8랭크)에 닿으면 원하는 기물로 바꿀 수 있습니다.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1726,7 +1726,7 @@
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>즉시, 룩의 가로와 세로 중 하나를 선택해 그 룩으로부터 4칸 이내에 있는 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
+          <t>즉시, 룩이 선 가로줄과 세로줄 중 하나를 골라 그 룩에서 4칸 이내의 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1767,7 +1767,7 @@
       <c r="E17" s="17" t="inlineStr"/>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>내 다음 2턴 동안, 적을 처치한 룩과 지정한 상대 기물 하나가 지정불가 상태가 됩니다.</t>
+          <t>룩이 적을 처치하면, 그 룩과 지정한 상대 기물 하나가 내 다음 2턴 동안 지정불가 상태가 됩니다.</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
@@ -1804,7 +1804,7 @@
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치하지는 못합니다.)</t>
+          <t>다음 1회, 지정한 아군 폰이 룩처럼 움직일 수 있습니다. (적을 처치할 수는 없습니다.)</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -1841,7 +1841,7 @@
       <c r="E19" s="17" t="inlineStr"/>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>다음 2턴 동안, 룩이 처치한 기물과 동일한 종류의 상대 기물을 모두 포영 상태로 만듭니다.</t>
+          <t>룩이 적을 처치하면, 그 기물과 같은 종류의 상대 기물이 모두 2턴 동안 포영됩니다.</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
@@ -1915,7 +1915,7 @@
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
+          <t>다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1956,7 +1956,7 @@
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
+          <t>다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1997,7 +1997,7 @@
       <c r="E23" s="17" t="inlineStr"/>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>지정한 아군 룩과 상대 폰의 위치를 교환합니다.</t>
+          <t>지정한 아군 룩과 지정한 상대 폰의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
@@ -2071,7 +2071,7 @@
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>게임 동안 한 번도 움직이지 않은 아군 기물을 선택하여 룩으로 만듭니다. (킹 제외)</t>
+          <t>게임 내내 한 번도 움직이지 않은 아군 기물 하나를 골라 룩으로 만듭니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -2112,7 +2112,7 @@
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>룩이 킹과 같은 가로열에 있다면 언제든지 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
+          <t>룩이 킹과 같은 가로줄에 있다면 언제든 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2190,7 +2190,7 @@
       <c r="E28" s="17" t="inlineStr"/>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>적을 처치한 나이트와 자신의 비숍 중 하나의 위치를 교환합니다.</t>
+          <t>나이트가 적을 처치할 때마다, 그 나이트와 아군 비숍 하나의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -2227,7 +2227,7 @@
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
+          <t>다음 1회, 나이트가 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -2268,7 +2268,7 @@
       <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>다음 2회, 나이트의 상·하·좌·우 어느 한 방향에 아군 폰이 있을 경우, 그 폰과 나이트의 위치를 바꿉니다.</t>
+          <t>다음 2회, 나이트의 상·하·좌·우 중 한 방향에 아군 폰이 있으면 그 폰과 나이트의 위치를 바꿉니다.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -2309,7 +2309,7 @@
       <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>다음 2턴 동안, 서로 나이트만 쓸 수 있습니다. (단, 체크 상태이거나 나이트가 없는 쪽은 일반적으로 움직일 수 있습니다.)</t>
+          <t>다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -2350,7 +2350,7 @@
       <c r="E32" s="6" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>지정한 아군 나이트의 좌우 1칸 모두에 적 기물이 있고 둘 다 나이트보다 기물점수가 높다면, 나이트가 두 기물 중 기물점수가 낮은 기물로 변이됩니다.</t>
+          <t>지정한 아군 나이트의 좌우 한 칸에 모두 적 기물이 있고 둘 다 나이트보다 점수가 높다면, 나이트가 둘 중 점수가 낮은 기물로 변이합니다.</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -2391,7 +2391,7 @@
       <c r="E33" s="6" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>나이트가 밟고 간 나와 상대방의 기물을 2턴 동안 포영 상태로 만듭니다. (킹 제외)</t>
+          <t>나이트가 지나간 칸에 있던 기물을 피아 구분 없이 2턴 동안 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -2432,7 +2432,7 @@
       <c r="E34" s="17" t="inlineStr"/>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>상대 나이트와 내 나이트의 위치가 가로·세로 모두 5칸 이상 차이날 경우, 상대 나이트를 처치합니다. (대상이 여러 개일 경우 자신이 선택)</t>
+          <t>상대 나이트가 내 나이트와 가로·세로 모두 5칸 이상 떨어져 있다면 그 나이트를 처치합니다. (대상이 여럿이면 내가 고릅니다.)</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
@@ -2469,7 +2469,7 @@
       <c r="E35" s="17" t="inlineStr"/>
       <c r="F35" s="17" t="inlineStr">
         <is>
-          <t>즉시, 나이트가 킹과 퀸을 제외한 상대의 가장 낮은 점수의 기물을 하나 없애고 그 위치로 이동합니다. (여러 개일 시 자신이 선택)</t>
+          <t>즉시, 나이트가 상대의 가장 낮은 점수 기물 하나를 없애고 그 자리로 이동합니다. (킹·퀸 제외. 대상이 여럿이면 내가 고릅니다.)</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
@@ -2506,7 +2506,7 @@
       <c r="E36" s="17" t="inlineStr"/>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>나이트를 2회 이상 강화한 상태라면, 비어있는 칸에 1턴 동안 지정불가 상태인 나이트를 2개 소환합니다.</t>
+          <t>나이트 증강을 2개 이상 가지고 있다면, 빈칸에 나이트 2개를 소환합니다. 소환된 나이트는 1턴 동안 지정불가입니다.</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
@@ -2584,7 +2584,7 @@
       <c r="E38" s="17" t="inlineStr"/>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>자신의 나이트가 살아있고 상대의 퀸이 살아있다면, 두 기물 모두 제거합니다.</t>
+          <t>아군 나이트와 상대 퀸이 모두 살아 있다면, 둘 다 제거합니다.</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 서로 교환합니다.</t>
+          <t>다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 두 폰의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>내 다음 2턴 동안, 비숍이 움직이지 못합니다. 그동안 비숍 주변 한 칸에 비숍이 서 있는 발판과 같은 색의 칸으로 적 기물이 온다면 그 기물을 제거합니다. (킹 제외)</t>
+          <t>내 다음 2턴 동안 비숍이 움직이지 못합니다. 그동안 비숍에 인접한 칸 중 비숍이 선 칸과 같은 색인 칸으로 적 기물이 오면 그 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="F41" s="17" t="inlineStr">
         <is>
-          <t>다음 상대의 2턴 동안 지정한 상대 폰이 한 번도 움직이지 않았을 경우, 그 폰을 제거합니다.</t>
+          <t>지정한 상대 폰이 상대의 다음 2턴 동안 한 번도 움직이지 않으면, 그 폰을 제거합니다.</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 홀수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
+          <t>1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 홀수라면 아군 진영 빈칸에 폰 하나를 소환합니다.</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 짝수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
+          <t>1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 짝수라면 아군 진영 빈칸에 폰 하나를 소환합니다.</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
+          <t>비숍이 적을 처치하고 2턴을 살아남으면, 잃었던 아군 기물 하나를 그 기물의 시작 칸에 되살립니다. (그 칸이 비어 있어야 합니다.)</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
-          <t>상대의 다음 2턴 동안, 비숍이 처치당할 경우 비숍을 처치한 상대 기물도 같이 죽습니다. (킹·퀸 제외)</t>
+          <t>상대의 다음 2턴 동안, 비숍이 처치당하면 그 비숍을 처치한 상대 기물도 함께 제거됩니다. (킹·퀸 제외)</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>상대의 다음 1턴 동안, 지정한 상대 기물이 움직이지 않는다면 제거됩니다. (킹·퀸 제외)</t>
+          <t>상대의 다음 1턴 동안 지정한 상대 기물이 움직이지 않으면, 그 기물을 제거합니다. (킹·퀸 제외)</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>다음 1회, 비숍이 상대 기물을 처치 시 그 기물 주위 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
+          <t>다음 1회, 비숍이 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>다음 1회 아군 킹이 체크를 당할 때, 체크를 한 기물을 1턴 동안 지정불가 상태로 만듭니다.</t>
+          <t>다음 1회, 아군 킹이 체크를 당하면 체크를 건 기물을 1턴 동안 지정불가 상태로 만듭니다.</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 죽은 상태라면 내 다음 3턴 동안, 비숍이 퀸처럼 움직일 수 있습니다.</t>
+          <t>아군 퀸이 잡힌 상태라면, 내 다음 3턴 동안 비숍이 퀸처럼 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="G49" s="17" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않는다면, 그 기물이 받고 있던 강화 효과가 모두 사라집니다.</t>
+          <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않으면, 그 기물이 받고 있던 증강 효과가 모두 사라집니다.</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -3141,7 +3141,7 @@
       <c r="E51" s="6" t="inlineStr"/>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>아군 퀸이 판의 긴 대각선(a1-h8 / a8-h1)에 해당하는 칸에 도착할 경우, 다음 턴에 그 대각선 위의 비어있는 칸 한 곳으로 순간이동할 수 있습니다.</t>
+          <t>아군 퀸이 판의 긴 대각선(a1–h8 / a8–h1) 칸에 도착하면, 다음 턴에 그 대각선 위의 빈칸 한 곳으로 순간이동할 수 있습니다.</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -3182,7 +3182,7 @@
       <c r="E52" s="17" t="inlineStr"/>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>내 다음 5턴 동안, 퀸이 상대 퀸과 함께 지정불가 상태가 됩니다.</t>
+          <t>내 다음 5턴 동안, 아군 퀸과 상대 퀸이 함께 지정불가 상태가 됩니다.</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
@@ -3219,7 +3219,7 @@
       <c r="E53" s="6" t="inlineStr"/>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>아군 퀸이 상대 퀸과 함께 제거됩니다. (양쪽 퀸이 모두 살아있을 때만 선택 가능)</t>
+          <t>아군 퀸과 상대 퀸을 함께 제거합니다. (양쪽 퀸이 모두 살아 있을 때만 고를 수 있습니다.)</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -3260,7 +3260,7 @@
       <c r="E54" s="6" t="inlineStr"/>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>자신과 상대가 지금까지 얻은 모든 강화 효과를 제거합니다. (이 강화 자신도 소멸하며, 이후 얻는 강화는 정상 적용됩니다.)</t>
+          <t>나와 상대가 지금까지 얻은 증강 효과를 모두 제거합니다. (이 증강도 함께 사라지며, 이후 얻는 증강은 정상 적용됩니다.)</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3301,7 +3301,7 @@
       <c r="E55" s="17" t="inlineStr"/>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>다음 1회, 다음 상대턴 동안 아군 퀸을 포영 상태로 만듭니다.</t>
+          <t>1회에 한해, 다음 상대턴 동안 아군 퀸을 포영시킵니다.</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
@@ -3338,7 +3338,7 @@
       <c r="E56" s="17" t="inlineStr"/>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>이 게임에서 아군 퀸을 상대방이 처치해도 상대의 처치 카운트에 더해지지 않습니다.</t>
+          <t>이 판에서 아군 퀸이 처치당해도 상대의 처치 수에 더해지지 않습니다.</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
@@ -3375,7 +3375,7 @@
       <c r="E57" s="6" t="inlineStr"/>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다. (킹 제외)</t>
+          <t>다음 상대턴 동안, 아군 퀸과 지정한 기물 하나를 함께 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -3416,7 +3416,7 @@
       <c r="E58" s="17" t="inlineStr"/>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>퀸을 1회 이상 강화한 상태라면, 퀸이 나이트처럼도 움직일 수 있습니다.</t>
+          <t>퀸 증강을 1개 이상 가지고 있다면, 퀸이 나이트처럼도 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -3453,7 +3453,7 @@
       <c r="E59" s="17" t="inlineStr"/>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 킹을 제외한 상대의 가장 높은 점수의 기물과 위치가 교환됩니다.</t>
+          <t>아군 퀸과, 킹을 제외한 상대의 가장 높은 점수 기물의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
@@ -3490,7 +3490,7 @@
       <c r="E60" s="6" t="inlineStr"/>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>퀸 주변 한 칸 내에 있는 모든 기물, 그리고 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
+          <t>퀸 주변 한 칸의 모든 기물과, 그 기물들과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3531,7 +3531,7 @@
       <c r="E61" s="6" t="inlineStr"/>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>아군 퀸이 2턴 동안 포영 상태가 되며, 그동안 포영된 위치에서 두 칸 이내에 상대 기물이 있을 경우 그 기물을 제거합니다. (킹 제외)</t>
+          <t>아군 퀸이 2턴 동안 포영되며, 그동안 포영된 자리에서 두 칸 이내에 들어온 상대 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -3572,7 +3572,7 @@
       <c r="E62" s="6" t="inlineStr"/>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>퀸이 어디에 있든 아군 킹 주변 한 칸 이내의 빈칸으로 움직일 수 있습니다.</t>
+          <t>퀸이 어디에 있든 아군 킹 주변 한 칸의 빈칸으로 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -3613,7 +3613,7 @@
       <c r="E63" s="17" t="inlineStr"/>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>다음 1회, 킹이 체크를 당한 경우 퀸과 킹의 위치를 바꿀 수 있습니다.</t>
+          <t>다음 1회, 킹이 체크를 당하면 퀸과 킹의 위치를 바꿀 수 있습니다.</t>
         </is>
       </c>
       <c r="G63" s="17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       <c r="E64" s="17" t="inlineStr"/>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>자신의 다음 강화에서 선택지를 두 개 고를 수 있습니다.</t>
+          <t>다음 증강을 고를 때 선택지를 두 개 고를 수 있습니다.</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -3687,7 +3687,7 @@
       <c r="E65" s="17" t="inlineStr"/>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>자신의 모든 제거를 처치로 간주합니다.</t>
+          <t>내가 일으킨 제거를 모두 처치로 셉니다.</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr">
@@ -3724,7 +3724,7 @@
       <c r="E66" s="6" t="inlineStr"/>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>나이트·비숍 중 한 기물의 6개 티어 증강 하나를 골라 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -3765,7 +3765,7 @@
       <c r="E67" s="17" t="inlineStr"/>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>상대 기물과 내 기물의 점수 차이만큼, 원하는 기물을 킹의 상하좌우에 배치할 수 있습니다. (상하좌우에 다른 기물이 있다면 그 칸에는 배치 불가)</t>
+          <t>상대와 나의 기물 점수 차이만큼 예산을 받아, 그만큼 원하는 기물을 킹의 상하좌우 빈칸에 배치합니다. (폰 1 · 나이트 3 · 비숍 3 · 룩 5 · 퀸 9점. 이미 기물이 있는 칸에는 배치할 수 없습니다.)</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr">
@@ -3802,7 +3802,7 @@
       <c r="E68" s="6" t="inlineStr"/>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>룩·퀸 중 한 기물의 11개 티어 증강 하나를 골라 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3843,7 +3843,7 @@
       <c r="E69" s="17" t="inlineStr"/>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>다음 1회, 다른 기물과 함께 킹을 한 번 움직일 수 있습니다.</t>
+          <t>다음 1회, 다른 기물을 움직인 뒤 킹도 한 번 더 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="G69" s="17" t="inlineStr">
@@ -3880,7 +3880,7 @@
       <c r="E70" s="6" t="inlineStr"/>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
+          <t>같은 기물의 증강을 2개 이상 가지고 있다면, 그 기물의 1개 티어 증강 하나를 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -3921,7 +3921,7 @@
       <c r="E71" s="6" t="inlineStr"/>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
+          <t>이미 가진 증강 하나를 골라, 같은 기물·같은 티어의 다른 증강으로 바꿉니다.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -3962,7 +3962,7 @@
       <c r="E72" s="17" t="inlineStr"/>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>킹이 아군 폰 하나를 상하로 지정한 위치까지 이동시킵니다. (기물을 넘어서는 갈 수 없습니다.)</t>
+          <t>킹이 아군 폰 하나를 위아래 방향으로 지정한 칸까지 옮깁니다. (다른 기물을 넘어갈 수는 없습니다.)</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
@@ -3999,7 +3999,7 @@
       <c r="E73" s="6" t="inlineStr"/>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
+          <t>이 증강을 얻은 뒤부터, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 차지하면 즉시 승리합니다.</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
@@ -4040,7 +4040,7 @@
       <c r="E74" s="17" t="inlineStr"/>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>서로의 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
+          <t>양쪽 킹을 제외한 모든 기물을 폰으로 변이시킵니다.</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>적을 처치한 폰의 전방 2칸 이내에 적 기물이 있을 시 교환합니다. 이때 상대 기물의 기물점수가 더 높다면 그 기물을 폰으로 변이시킵니다. (킹 제외)</t>
+          <t>폰이 적을 처치하면, 그 폰 앞 2칸 이내에 있는 적 기물 하나와 위치를 교환합니다. 그 기물의 점수가 폰보다 높다면 폰으로 변이시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>모든 폰이 2칸씩 행동(이동 및 처치)할 수 있습니다. (중간 칸에 기물이 있으면 통과할 수 없습니다.)</t>
+          <t>모든 폰이 한 번에 두 칸까지 움직이고 처치할 수 있습니다. (지나갈 칸에 기물이 있으면 통과하지 못합니다.)</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>폰이 꼭 반대편 끝이 아니더라도, 어느 한 방향의 끝(a·h파일 또는 1·8랭크)에 도달한다면 폰을 원하는 기물로 바꿀 수 있습니다.</t>
+          <t>폰이 반대편 끝이 아니어도, 판의 어느 한쪽 끝(a·h파일 또는 1·8랭크)에 닿으면 원하는 기물로 바꿀 수 있습니다.</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>즉시, 룩의 가로와 세로 중 하나를 선택해 그 룩으로부터 4칸 이내에 있는 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
+          <t>즉시, 룩이 선 가로줄과 세로줄 중 하나를 골라 그 룩에서 4칸 이내의 모든 기물을 제거합니다. (아군 포함, 해당 룩과 양측 킹은 제외)</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
+          <t>다음 상대턴 동안, 상대는 기준 룩보다 위쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (상대 룩이 여럿이면 상대가 기준 룩을 하나 고릅니다. 룩이 없으면 효과 없음. 체크를 벗어나는 수는 제한되지 않습니다.)</t>
+          <t>다음 상대턴 동안, 상대는 기준 룩보다 아래쪽으로 기물을 움직일 수 없습니다. (기준 룩은 상대가 자기 룩 중에서 하나 고릅니다. 상대에게 룩이 없으면 효과가 없고, 체크를 벗어나는 수는 막지 않습니다.)</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>게임 동안 한 번도 움직이지 않은 아군 기물을 선택하여 룩으로 만듭니다. (킹 제외)</t>
+          <t>게임 내내 한 번도 움직이지 않은 아군 기물 하나를 골라 룩으로 만듭니다. (킹 제외)</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>룩이 킹과 같은 가로열에 있다면 언제든지 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
+          <t>룩이 킹과 같은 가로줄에 있다면 언제든 캐슬링을 할 수 있습니다. (이동 이력·경로·체크 조건을 무시합니다.)</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>다음 1회, 적을 처치한 나이트의 한 칸 주변에 있는 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
+          <t>다음 1회, 나이트가 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (아군 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>다음 2회, 나이트의 상·하·좌·우 어느 한 방향에 아군 폰이 있을 경우, 그 폰과 나이트의 위치를 바꿉니다.</t>
+          <t>다음 2회, 나이트의 상·하·좌·우 중 한 방향에 아군 폰이 있으면 그 폰과 나이트의 위치를 바꿉니다.</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>다음 2턴 동안, 서로 나이트만 쓸 수 있습니다. (단, 체크 상태이거나 나이트가 없는 쪽은 일반적으로 움직일 수 있습니다.)</t>
+          <t>다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>지정한 아군 나이트의 좌우 1칸 모두에 적 기물이 있고 둘 다 나이트보다 기물점수가 높다면, 나이트가 두 기물 중 기물점수가 낮은 기물로 변이됩니다.</t>
+          <t>지정한 아군 나이트의 좌우 한 칸에 모두 적 기물이 있고 둘 다 나이트보다 점수가 높다면, 나이트가 둘 중 점수가 낮은 기물로 변이합니다.</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>나이트가 밟고 간 나와 상대방의 기물을 2턴 동안 포영 상태로 만듭니다. (킹 제외)</t>
+          <t>나이트가 지나간 칸에 있던 기물을 피아 구분 없이 2턴 동안 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="F17" s="17" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 서로 교환합니다.</t>
+          <t>다음 1회, 4~5랭크에 내 폰과 상대 폰이 모두 있다면 두 폰의 위치를 교환합니다.</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>내 다음 2턴 동안, 비숍이 움직이지 못합니다. 그동안 비숍 주변 한 칸에 비숍이 서 있는 발판과 같은 색의 칸으로 적 기물이 온다면 그 기물을 제거합니다. (킹 제외)</t>
+          <t>내 다음 2턴 동안 비숍이 움직이지 못합니다. 그동안 비숍에 인접한 칸 중 비숍이 선 칸과 같은 색인 칸으로 적 기물이 오면 그 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 홀수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
+          <t>1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 홀수라면 아군 진영 빈칸에 폰 하나를 소환합니다.</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>1턴 뒤 내 차례에, 자신의 남은 기물의 기물점수 합이 짝수인 경우 폰 하나를 아군 진영 빈칸에 소환합니다.</t>
+          <t>1턴 뒤 내 차례에, 남은 아군 기물의 점수 합이 짝수라면 아군 진영 빈칸에 폰 하나를 소환합니다.</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>적을 처치한 비숍이 2턴 동안 살아있을 경우, 자신의 처치된 기물 중 하나를 스폰 위치에 소환합니다. (그 자리에 다른 기물이 있을 경우 불가)</t>
+          <t>비숍이 적을 처치하고 2턴을 살아남으면, 잃었던 아군 기물 하나를 그 기물의 시작 칸에 되살립니다. (그 칸이 비어 있어야 합니다.)</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>다음 1회, 비숍이 상대 기물을 처치 시 그 기물 주위 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
+          <t>다음 1회, 비숍이 적을 처치하면 그 자리 주변 한 칸의 모든 기물을 제거합니다. (양측 킹 제외)</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않는다면, 그 기물이 받고 있던 강화 효과가 모두 사라집니다.</t>
+          <t>지정한 상대 기물이 상대의 다음 2턴 동안 처치·제거되지 않으면, 그 기물이 받고 있던 증강 효과가 모두 사라집니다.</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 판의 긴 대각선(a1-h8 / a8-h1)에 해당하는 칸에 도착할 경우, 다음 턴에 그 대각선 위의 비어있는 칸 한 곳으로 순간이동할 수 있습니다.</t>
+          <t>아군 퀸이 판의 긴 대각선(a1–h8 / a8–h1) 칸에 도착하면, 다음 턴에 그 대각선 위의 빈칸 한 곳으로 순간이동할 수 있습니다.</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 상대 퀸과 함께 제거됩니다. (양쪽 퀸이 모두 살아있을 때만 선택 가능)</t>
+          <t>아군 퀸과 상대 퀸을 함께 제거합니다. (양쪽 퀸이 모두 살아 있을 때만 고를 수 있습니다.)</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>자신과 상대가 지금까지 얻은 모든 강화 효과를 제거합니다. (이 강화 자신도 소멸하며, 이후 얻는 강화는 정상 적용됩니다.)</t>
+          <t>나와 상대가 지금까지 얻은 증강 효과를 모두 제거합니다. (이 증강도 함께 사라지며, 이후 얻는 증강은 정상 적용됩니다.)</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>다음 상대턴 동안, 아군 퀸과 지정된 기물 하나를 포영시킵니다. (킹 제외)</t>
+          <t>다음 상대턴 동안, 아군 퀸과 지정한 기물 하나를 함께 포영시킵니다. (킹 제외)</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>퀸 주변 한 칸 내에 있는 모든 기물, 그리고 그 기물과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
+          <t>퀸 주변 한 칸의 모든 기물과, 그 기물들과 같은 종류의 기물을 모두 제거합니다. (퀸 자신 포함, 양측 킹 제외)</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>아군 퀸이 2턴 동안 포영 상태가 되며, 그동안 포영된 위치에서 두 칸 이내에 상대 기물이 있을 경우 그 기물을 제거합니다. (킹 제외)</t>
+          <t>아군 퀸이 2턴 동안 포영되며, 그동안 포영된 자리에서 두 칸 이내에 들어온 상대 기물을 제거합니다. (킹 제외)</t>
         </is>
       </c>
       <c r="F31" s="17" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>퀸이 어디에 있든 아군 킹 주변 한 칸 이내의 빈칸으로 움직일 수 있습니다.</t>
+          <t>퀸이 어디에 있든 아군 킹 주변 한 칸의 빈칸으로 움직일 수 있습니다.</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>나이트, 비숍 중 한 기물의 3번째 강화(6개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>나이트·비숍 중 한 기물의 6개 티어 증강 하나를 골라 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>룩, 퀸 중 한 기물의 4번째 강화(11개 티어) 효과를 선택해 추가로 얻습니다.</t>
+          <t>룩·퀸 중 한 기물의 11개 티어 증강 하나를 골라 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>지금까지 같은 종류의 기물을 2회 이상 강화했다면, 그 기물의 1개 티어 강화 효과 중 하나를 추가로 얻습니다.</t>
+          <t>같은 기물의 증강을 2개 이상 가지고 있다면, 그 기물의 1개 티어 증강 하나를 추가로 얻습니다.</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>이미 보유한 강화 하나를 선택해, 같은 기물·같은 티어의 다른 강화로 교체합니다.</t>
+          <t>이미 가진 증강 하나를 골라, 같은 기물·같은 티어의 다른 증강으로 바꿉니다.</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>이 강화 이후, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 점거하면 즉시 승리합니다.</t>
+          <t>이 증강을 얻은 뒤부터, 아군 기물이 상대 킹의 상하좌우 4칸 중 3칸을 동시에 차지하면 즉시 승리합니다.</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr">

--- a/docs/무제체스_증강표_v2.xlsx
+++ b/docs/무제체스_증강표_v2.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>[Q3b] 1회에 한해, 다음 상대턴 동안 아군 퀸을 포영시킵니다.</t>
+          <t>[Q3b] 증강을 얻는 즉시, 아군 퀸이 다음 상대턴 동안 포영됩니다.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -3301,7 +3301,7 @@
       <c r="E55" s="17" t="inlineStr"/>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>1회에 한해, 다음 상대턴 동안 아군 퀸을 포영시킵니다.</t>
+          <t>증강을 얻는 즉시, 아군 퀸이 다음 상대턴 동안 포영됩니다.</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">

--- a/docs/무제체스_증강표_v2.xlsx
+++ b/docs/무제체스_증강표_v2.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>[N3b] 다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
+          <t>[N3b] 양쪽이 한 턴씩 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -2309,7 +2309,7 @@
       <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
+          <t>양쪽이 한 턴씩 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>다음 2턴 동안, 양쪽 모두 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
+          <t>양쪽이 한 턴씩 나이트만 움직일 수 있습니다. (체크 상태이거나 나이트가 없는 쪽은 평소대로 움직입니다.)</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">

--- a/docs/무제체스_증강표_v2.xlsx
+++ b/docs/무제체스_증강표_v2.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="증강표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="증강목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정내역" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전역룰" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용어해설" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="밸런스메모" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="증강표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="증강목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="개정내역" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="전역룰" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="용어해설" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="밸런스메모" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'증강목록'!$A$1:$I$74</definedName>
@@ -575,7 +575,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>처치 카운트가 1 · 3 · 6 · 11 에 도달하면 해당 티어의 증강 18개 중 무작위 3개를 제시받고 1개를 획득합니다. 분홍색 배경 = 원안에서 수정된 증강 (수정 사유는 '개정내역' 시트 참고).</t>
+          <t>처치 카운트가 1 · 3 · 6 · 11 에 도달하면, 그 처치를 해낸 기물의 칸(기물 × 티어)에 있는 선택지 3개가 그대로 펼쳐지고 그중 1개를 획득합니다. 분홍색 배경 = 원안에서 수정된 증강 (수정 사유는 '개정내역' 시트 참고).</t>
         </is>
       </c>
     </row>
